--- a/data/analysis_gemini_2_5_flash_no_reid/visual_event_eval_gemini_2_5_flash_no_reid.xlsx
+++ b/data/analysis_gemini_2_5_flash_no_reid/visual_event_eval_gemini_2_5_flash_no_reid.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="46">
   <si>
     <t>event</t>
   </si>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1856,7 +1856,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1927,6 +1927,23 @@
         <v>22</v>
       </c>
     </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
